--- a/customer_data.xlsx
+++ b/customer_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RAHIL KHAN\HSBC\FaceCard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mrsat\OneDrive\Desktop\FaceCard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8EE93F8-8220-4160-9032-AF3D158CF834}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E994E133-491F-42AA-9BF2-9B505B1977CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-107" yWindow="-107" windowWidth="20847" windowHeight="11111" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Cust_ID</t>
   </si>
@@ -40,6 +40,9 @@
   </si>
   <si>
     <t>Phone</t>
+  </si>
+  <si>
+    <t>Rahil Khan</t>
   </si>
 </sst>
 </file>
@@ -357,11 +360,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.8984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -392,6 +395,20 @@
         <v>6398695799</v>
       </c>
     </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>22122141</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <v>2345</v>
+      </c>
+      <c r="D3">
+        <v>9963293874</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
